--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,12 +483,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -496,24 +496,24 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -523,8 +523,8 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -851,10 +851,8 @@
           <t>Sudip Kandel</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9865125447</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9865125447</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9865125447</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9865125447</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.66369</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.66369</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,48 +938,243 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33823</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33823</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>5d 19m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>5d 19m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362110</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9866494523</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9869365032R</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:12:39 PM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Eresha cafe and restaurant - Family restaurant Kharibot Chowk Kharibot, , ,</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>Premkarki440@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1039,7 +1228,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1125,7 +1314,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1183,7 +1372,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1048,10 +1048,8 @@
           <t>Prem Bahadur Karki</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9866494523</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9866494523</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1137,10 +1135,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1151,7 +1147,7 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,10 +517,10 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1171,6 +1171,217 @@
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364290</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9802301403</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33:20 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9802301403</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:44:56 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33:20 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.70941</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Gyaneshwor Marg NIC Asia Bank Limited, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>hardwarecenterthecarpenter@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>01:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB426</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.329</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1h 48m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1187,20 +1398,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1224,7 +1435,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1234,7 +1445,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1245,7 +1456,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1468,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1480,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
@@ -1310,14 +1521,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1368,14 +1579,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1451,6 +1662,73 @@
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364290</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33:20 PM</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:44:56 AM</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33:20 PM</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="31" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1243,10 +1243,8 @@
           <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9802301403</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9802301403</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1281,10 +1279,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.70941</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.70941</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1340,48 +1336,462 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB426</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.329</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.32899999999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1h 48m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363561</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Jiwan Kapali</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Jiwan Kapali</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841443943</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841443943</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:04:20 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.7028</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Tilganga , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>06:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L51-7</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.3505</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>20h 55m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359513</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Chhetri Baniya</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Chhetri Baniya</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841808549</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53:37 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841808549</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:03:46 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53:37 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.75558</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>suryadarshan height baniyatar tokha-3 kathmandu bagmat, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>laxmibaniya20@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>13:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L12-4</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.3208</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 49m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1398,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1435,7 +1845,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1445,7 +1855,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1456,7 +1866,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1890,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1h 48m</t>
+          <t>1d 14h 51m</t>
         </is>
       </c>
     </row>
@@ -1521,14 +1931,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1579,14 +1989,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1698,14 +2108,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 12:33:20 PM</t>
@@ -1729,6 +2139,140 @@
       <c r="M18" s="3" t="inlineStr">
         <is>
           <t>1h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363561</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Jiwan Kapali</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:04:20 PM</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>20h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359513</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Chhetri Baniya</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53:37 PM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:03:46 PM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53:37 PM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1446,10 +1446,8 @@
           <t>Jiwan Kapali</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841443943</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841443943</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1484,10 +1482,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.7028</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.7028</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1539,25 +1535,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L51-7</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.3505</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.3505</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1653,10 +1645,8 @@
           <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841808549</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841808549</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1691,10 +1681,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.75558</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.75558</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1750,25 +1738,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L12-4</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.3208</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.32080000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1817,7 +1801,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2175,7 +2159,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2242,7 +2226,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -506,19 +506,19 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="39" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1776,6 +1776,619 @@
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>NETTV issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364261</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9826039231</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:09:13 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>KLK9826039231</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:23:09 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:20:24 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Dallu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>triratna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>2h 11m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>2h 57m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:29 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361889</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Kalim Ansari</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Kalim Ansari</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9851079204</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:10:39 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851079204</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:10:39 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:29:52 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.690312</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near to Jhapali store , Baneshor , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>kalimansari449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L11-3</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.349812</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>2d 19m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2d 19m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:26 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9741716174</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:26:08 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>CHB9741716174</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:26:08 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>New baneswor, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9741716174@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>19:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>4d 5h 16m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1792,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1801,7 +2414,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1829,7 +2442,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1839,7 +2452,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1850,7 +2463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +2487,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 51m</t>
+          <t>2d 6h 27m</t>
         </is>
       </c>
     </row>
@@ -1915,348 +2528,456 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="C15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TKT1363561</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Jiwan Kapali</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>20h 55m</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>TKT1364290</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33:20 PM</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:44:56 AM</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:33:20 PM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>1h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363561</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Jiwan Kapali</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:04:20 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>20h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>TKT1359513</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>3d 21h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358878</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Tanisha giri</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:26:08 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 08:09:51 AM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:26:08 PM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,12 +496,12 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -534,7 +534,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1848,10 +1848,8 @@
           <t>Niratna manandhar</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9826039231</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9826039231</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1937,10 +1935,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1951,7 +1947,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2047,10 +2043,8 @@
           <t>Kalim Ansari</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9851079204</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9851079204</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2085,10 +2079,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.690312</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.690312</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2140,25 +2132,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L11-3</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.349812</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.349812</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 Router  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2254,10 +2242,8 @@
           <t>Tanisha giri</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9741716174</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9741716174</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2329,10 +2315,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2351,10 +2335,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2365,32 +2347,1063 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>4d 5h 16m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>4d 5h 16m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361677</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9851095178</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9851225178</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:39:26 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.719963</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Naya Bazaar-16, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>overseas.saving67@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>22:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.308453</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 27m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 27m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:40 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:40:00 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>4d 23h 32m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>4d 23h 32m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363186</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Michael Chaudhary</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Michael Chaudhary</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9860680209</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:42:07 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9860680209</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:42:07 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:36:39 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.70694</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Banglamukhi Temple,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>michaelchaudhary143@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>11:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB111</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.26992</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 54m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 54m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:30 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9844750444</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9844750444</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Near By SitaRams Gokul Milks Pvt. Ltd. - Milk delivery service M775+9H3 Kirtipur 44618, Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>08:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:29 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9844750444</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9844750444</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Near By SitaRams Gokul Milks Pvt. Ltd. - Milk delivery service M775+9H3 Kirtipur 44618, Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>08:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2405,13 +3418,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -2442,7 +3455,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2452,7 +3465,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2463,7 +3476,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +3488,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h 42m</t>
         </is>
       </c>
     </row>
@@ -2487,7 +3500,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 6h 27m</t>
+          <t>2d 7h 29m</t>
         </is>
       </c>
     </row>
@@ -2528,14 +3541,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2557,305 +3570,212 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1363561</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Jiwan Kapali</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>20h 55m</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2885,22 +3805,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2910,74 +3830,476 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>TKT1363561</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Jiwan Kapali</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 04:04:20 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:59:31 PM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>20h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359513</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Chhetri Baniya</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53:37 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:03:46 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:53:37 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1358878</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Tanisha giri</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>4d 5h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361677</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:11:48 AM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:39:26 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 27m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363186</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Michael Chaudhary</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:42:07 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:42:07 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:36:39 PM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 54m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2443,10 +2443,8 @@
           <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9851095178</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9851095178</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2481,10 +2479,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.719963</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.719963</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2540,25 +2536,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.308453</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.308453</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2654,10 +2646,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2692,10 +2682,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.699563</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.699563</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2747,25 +2735,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2861,10 +2845,8 @@
           <t>Michael Chaudhary</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9860680209</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9860680209</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2899,10 +2881,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.70694</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.70694</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2940,10 +2920,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH12" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
@@ -2962,25 +2940,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB111</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.26992</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.26992</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3066,20 +3040,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Ganesh Pokhrel</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9844750444</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9844750444</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3165,10 +3133,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3179,7 +3145,7 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3265,20 +3231,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Ganesh Pokhrel</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9844750444</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9844750444</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3364,10 +3324,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3378,32 +3336,445 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>3d 39m</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>3d 2h 52m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360556</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Dal Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Dal Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9886381078</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:53:50 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9841634104</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:43:47 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:53:50 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Near to Banasthali Powerhouse, P7GW+F4G, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>07:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB273</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 10m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:55 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr"/>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 1:48 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr"/>
+      <c r="V17" s="3" t="inlineStr"/>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="inlineStr"/>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr"/>
+      <c r="AA17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr"/>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
+      <c r="AM17" s="3" t="inlineStr"/>
+      <c r="AN17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3455,7 +3826,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3465,7 +3836,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3476,7 +3847,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3859,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 42m</t>
+          <t>1d 37m</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3871,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 7h 29m</t>
+          <t>2d 9h 27m</t>
         </is>
       </c>
     </row>
@@ -3541,14 +3912,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -3588,328 +3959,223 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1363561</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Jiwan Kapali</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>20h 55m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3939,22 +4205,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3964,19 +4230,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1363561</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Jiwan Kapali</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4006,22 +4272,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>08 Oct 2026 04:04:20 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4031,19 +4297,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>4d 5h 16m</t>
+          <t>20h 55m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1361677</t>
+          <t>TKT1359513</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Overseas Saving and Credit Co-operative Ltd</t>
+          <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4058,59 +4324,59 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:39:26 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1363186</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Michael Chaudhary</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4125,69 +4391,69 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:36:39 PM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1361677</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4202,104 +4468,305 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:39:26 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1363186</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Michael Chaudhary</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:42:07 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:42:07 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:36:39 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 54m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1360357</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Ganesh Pokhrel</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>06 Oct 2026 12:50:59 PM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>06 Oct 2026 10:37:52 AM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 01:30:16 PM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>3d 39m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>3d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360556</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Dal Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:53:50 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:43:47 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:53:50 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 10m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -3432,10 +3432,8 @@
           <t>Dal Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9886381078</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9886381078</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3470,10 +3468,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3525,25 +3521,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB273</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3778,6 +3770,209 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>ssid not shown</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361686</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Mishra</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Mishra</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9708052945</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:07:14 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708052945</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:15:14 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:07:14 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Kia Nepal - Gairidhara Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>aabhi_mishra@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>22:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3789,12 +3984,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -3826,7 +4021,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3836,7 +4031,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3847,7 +4042,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +4054,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 37m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
@@ -3871,7 +4066,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 9h 27m</t>
+          <t>2d 8h 47m</t>
         </is>
       </c>
     </row>
@@ -3926,150 +4121,145 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>63.6%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -4078,238 +4268,150 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1363561</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Jiwan Kapali</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>20h 55m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4339,22 +4441,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4364,19 +4466,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1363561</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Jiwan Kapali</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4406,22 +4508,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>08 Oct 2026 04:04:20 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4431,19 +4533,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>4d 5h 16m</t>
+          <t>20h 55m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1361677</t>
+          <t>TKT1359513</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Overseas Saving and Credit Co-operative Ltd</t>
+          <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4458,12 +4560,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4473,44 +4575,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:39:26 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1363186</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Michael Chaudhary</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4525,12 +4627,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -4540,54 +4642,54 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:36:39 PM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1361677</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4607,54 +4709,54 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:39:26 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1363186</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Michael Chaudhary</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4674,99 +4776,300 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:36:39 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360357</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Ganesh Pokhrel</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 12:50:59 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:37:52 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:30:16 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>3d 39m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>3d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>TKT1360556</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Dal Bahadur Thapa</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>06 Oct 2026 12:43:47 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>3d 1h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361686</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Abhishek Mishra</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:07:14 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:15:14 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:07:14 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,13 +483,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -524,7 +524,7 @@
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -3837,10 +3837,8 @@
           <t>Abhishek Mishra</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9708052945</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9708052945</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3930,10 +3928,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -3944,32 +3940,665 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : ssid not shown   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:16 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361912</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Ram Prasad Adhikari</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Ram Prasad Adhikari</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9857050309</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:06 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9857050309</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:27:33 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:06 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.653141</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Satdobato Godawari Sadak Lalitpur 44700,Near Little Angels’ School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>rampd821@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>20:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.338066</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 52m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 48m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:16 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364308</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9841593085</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9869319501</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:14 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.68906</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>P863+PJV, Purano Dhalko Marg, Kathmandu 44600 Near by Dhalko Cold Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>ritikagrawaldtu@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>03:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.29544</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:15 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364308</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9841593085</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9869319501</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:14 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.68906</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>P863+PJV, Purano Dhalko Marg, Kathmandu 44600 Near by Dhalko Cold Store, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>ritikagrawaldtu@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>03:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.29544</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3984,7 +4613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4021,7 +4650,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -4031,7 +4660,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -4042,7 +4671,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4683,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 10m</t>
+          <t>17h 33m</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4695,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 8h 47m</t>
+          <t>1d 23h 57m</t>
         </is>
       </c>
     </row>
@@ -4107,14 +4736,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -4233,14 +4862,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -5039,14 +5668,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>Case : ssid not shown   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 02:07:14 PM</t>
@@ -5070,6 +5699,207 @@
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t>2d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361912</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Ram Prasad Adhikari</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:06 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 01:27:33 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:06 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2d 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364308</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:14 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364308</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:14 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW21"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4036,10 +4036,8 @@
           <t>Ram Prasad Adhikari</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9857050309</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9857050309</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4074,10 +4072,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.653141</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.653141</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4133,25 +4129,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.338066</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.338066</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4247,10 +4239,8 @@
           <t>Ritik Agrawal</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9841593085</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9841593085</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4285,10 +4275,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.68906</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.68906</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -4344,25 +4332,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.29544</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.29544</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4458,10 +4442,8 @@
           <t>Ritik Agrawal</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9841593085</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9841593085</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4496,10 +4478,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.68906</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.68906</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4555,48 +4535,251 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.29544</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.29544</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>3h 16m</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>3h 16m</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:21 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362712</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Gautam</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Gautam</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9843649578</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:21:11 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9818214299</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 09:15:31 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:21:11 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.70658</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>khadka gau miteri chowk, Near by kankali school , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>14:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.25989</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 5m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4613,7 +4796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4650,7 +4833,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -4660,7 +4843,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4671,7 +4854,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4866,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 33m</t>
+          <t>16h 18m</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4878,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 57m</t>
+          <t>1d 23h 27m</t>
         </is>
       </c>
     </row>
@@ -4736,14 +4919,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -4862,14 +5045,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5918,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -5802,7 +5985,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -5869,14 +6052,14 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 10:59:15 AM</t>
@@ -5900,6 +6083,73 @@
       <c r="M38" s="3" t="inlineStr">
         <is>
           <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362712</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Shyam Gautam</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:21:11 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 09:15:31 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:21:11 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 17h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4645,10 +4645,8 @@
           <t>Shyam Gautam</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9843649578</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9843649578</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4683,10 +4681,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.70658</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.70658</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4738,48 +4734,673 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.25989</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.25989</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 5m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:41 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>stbbox issue</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362011</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9848949572</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:57:24 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9848949572</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:22:05 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:41:21 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Khadka Gaun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>9811155449@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>20:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 43m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>2d 19m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:47 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363498</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Unnati Hardware and suppliers</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Unnati Hardware and suppliers</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851326047</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:47:31 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9801057800</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:20:49 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:47:31 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.68714</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>M8PG+324, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>laxmangupta13@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>09:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.31918</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>1d 17h 5m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>23h 26m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW22" s="3" t="inlineStr">
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:33 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363317</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Amal Shrestha</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Amal Shrestha</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9861493857</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:33:28 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9861493857</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:29 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:33:28 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.72273</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu,Mid Baneshwor-10 Lakhe Chaur Marg,Devokta Sadak,Opposite to NIC ASIA Bank, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>amoolshrestha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>11:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB036</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.31391</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 32m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4796,7 +5417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4833,7 +5454,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4843,7 +5464,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4854,7 +5475,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -4866,7 +5487,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 18m</t>
+          <t>16h 14m</t>
         </is>
       </c>
     </row>
@@ -4878,7 +5499,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 27m</t>
+          <t>1d 20h 48m</t>
         </is>
       </c>
     </row>
@@ -4919,14 +5540,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -4937,10 +5558,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -5045,14 +5666,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5685,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -5082,215 +5703,171 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1363561</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Jiwan Kapali</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5320,22 +5897,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5345,19 +5922,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>20h 55m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1363561</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Jiwan Kapali</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5387,22 +5964,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>08 Oct 2026 04:04:20 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -5412,19 +5989,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>20h 55m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1359513</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5454,22 +6031,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5479,19 +6056,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>4d 5h 16m</t>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1361677</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Overseas Saving and Credit Co-operative Ltd</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5506,12 +6083,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5521,44 +6098,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:39:26 PM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1363186</t>
+          <t>TKT1361677</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Michael Chaudhary</t>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5588,54 +6165,54 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:36:39 PM</t>
+          <t>09 Oct 2026 01:39:26 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1363186</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Michael Chaudhary</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5655,32 +6232,32 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:36:39 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
     </row>
@@ -5754,32 +6331,32 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1360556</t>
+          <t>TKT1360357</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Dal Bahadur Thapa</t>
+          <t>Ganesh Pokhrel</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5789,54 +6366,54 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>06 Oct 2026 12:50:59 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:43:47 PM</t>
+          <t>06 Oct 2026 10:37:52 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>09 Oct 2026 01:30:16 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 39m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>3d 1h 10m</t>
+          <t>3d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1361686</t>
+          <t>TKT1360556</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Abhishek Mishra</t>
+          <t>Dal Bahadur Thapa</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -5856,22 +6433,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:15:14 AM</t>
+          <t>06 Oct 2026 12:43:47 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -5881,29 +6458,29 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>3d 1h 10m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1361912</t>
+          <t>TKT1361686</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ram Prasad Adhikari</t>
+          <t>Abhishek Mishra</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -5923,22 +6500,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:27:33 PM</t>
+          <t>07 Oct 2026 11:15:14 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -5948,19 +6525,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 48m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1364308</t>
+          <t>TKT1361912</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Ritik Agrawal</t>
+          <t>Ram Prasad Adhikari</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -5975,12 +6552,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -5990,32 +6567,32 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>07 Oct 2026 01:27:33 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:14 PM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>2d 48m</t>
         </is>
       </c>
     </row>
@@ -6089,67 +6666,335 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>TKT1364308</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Ritik Agrawal</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:59:15 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:16:14 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>3h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>TKT1362712</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Shyam Gautam</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>07 Oct 2026 09:15:31 PM</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>1d 17h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362011</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Shivaraj Ojhaya  Tharu</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:57:24 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:22:05 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:41:21 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 43m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>2d 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363498</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Unnati Hardware and suppliers</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:47:31 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 03:20:49 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:47:31 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>23h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363317</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Amal Shrestha</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:33:28 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:29 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:33:28 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -527,7 +527,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -4844,10 +4844,8 @@
           <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9848949572</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9848949572</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4937,10 +4935,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4951,7 +4947,7 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5047,10 +5043,8 @@
           <t>Unnati Hardware and suppliers</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851326047</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851326047</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5085,10 +5079,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.68714</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.68714</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5144,25 +5136,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.31918</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.31918</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5258,10 +5246,8 @@
           <t>Amal Shrestha</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9861493857</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9861493857</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5296,10 +5282,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.72273</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.72273</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5337,10 +5321,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
@@ -5359,50 +5341,460 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB036</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.31391</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.31391000000001</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 32m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360970</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Roshan lamichhane</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Roshan lamichhane</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9840296952</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:55:06 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9840296952</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:43:34 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:55:06 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Spring valley academy - School Q864+683 Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>ithmine580@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>04:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L57-1</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 32m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 11m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW25" s="3" t="inlineStr">
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 2:54 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>POWER ISSUE</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360101</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Suman Neupane</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Suman Neupane</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851228447</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:54:41 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>BKT9851228447</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 07:08:33 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:54:41 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.666501544712574</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>bkt suryabinayek harsa chowk, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>human@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>10:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L6-1</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.40531158447267</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>3d 7h 46m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5454,7 +5846,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -5464,7 +5856,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5475,7 +5867,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5879,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 14m</t>
+          <t>14h 31m</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5891,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 48m</t>
+          <t>1d 23h 59m</t>
         </is>
       </c>
     </row>
@@ -5540,14 +5932,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -5666,14 +6058,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -6830,7 +7222,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -6897,7 +7289,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -6964,14 +7356,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 02:33:28 PM</t>
@@ -6995,6 +7387,140 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>1d 1h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360970</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Roshan lamichhane</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:55:06 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:43:34 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:55:06 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1360101</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Suman Neupane</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:54:41 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 07:08:33 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:54:41 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>3d 7h 46m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5451,10 +5451,8 @@
           <t>Roshan lamichhane</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9840296952</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9840296952</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5544,10 +5542,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -5558,7 +5554,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5654,10 +5650,8 @@
           <t>Suman Neupane</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851228447</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851228447</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5692,10 +5686,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.666501544712574</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.66650154471257</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5751,50 +5743,252 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>L6-1</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.40531158447267</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.40531158447267</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>3d 7h 46m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>3d 7h 46m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:10 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:07 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="AA29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AC29" s="3" t="inlineStr"/>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr"/>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -5818,7 +6012,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5846,7 +6040,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -5867,7 +6061,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7617,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7490,7 +7684,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5992,6 +5992,109 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 UPGRADE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="AA30" s="3" t="inlineStr"/>
+      <c r="AB30" s="3" t="inlineStr"/>
+      <c r="AC30" s="3" t="inlineStr"/>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr"/>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr"/>
+      <c r="AN30" s="3" t="inlineStr"/>
+      <c r="AO30" s="3" t="inlineStr"/>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6 UPGRADE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6040,7 +6143,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -6061,7 +6164,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,10 +494,10 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -523,16 +523,16 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -6095,6 +6095,1881 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364274</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Chhow Maya Tamang</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Chhow Maya Tamang</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9745383806</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:45:40 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9745383806</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:18 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:45:40 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>near by Nakkhu Dobato - Housing society M894+HG6 Machhindra Nath Sadak Lalitpur 44600, Bagmati, Nepa</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>05:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:45 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:08:34 AM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:45:54 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Near lkapuri Colony - Housing society P8Q9+WVH Prayas marg Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>1d 9h 37m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>5d 6h 54m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:42 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361815</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Mangal das shrestha</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Mangal das shrestha</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9742468574</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:40 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9842468574</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:31:41 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:40 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.74281</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Shreetol Marg, Kathmandu near Prithwi Secondary Boarding School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>Shresthadas2021@outlook.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>23:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>L8-2</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.33132</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 10m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:32 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364471</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Sujit Shrestha</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Sujit Shrestha</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9849838775</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:32:27 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9849838775</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:52:21 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:32:27 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.744333</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Ishan Children &amp; Women's Hospital Pvt. Ltd. - Hospital Kalkinarayan Tole Kathmandu 44600, Bagmati, C</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>sujeetstha567@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>02:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L1-7</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.332844</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2h 40m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>SLOW ISSUE</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363149</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>dipal shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>dipal shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9851234306</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:38:37 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851234306</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:20:05 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:38:37 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>27.715176751304764, 85.30123539310843, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>9851234306@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>14:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 18m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:36 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Device recovery</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361538</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Timsina</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Timsina</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9844641620</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Refund Request</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9844641620</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 09:57:52 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.71277</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Refund Request</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>bodegal tole bhagwanpau swyambhu near arunodhaya school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>sarojtimsina5131@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Refundable Deposit</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>01:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.29517</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 38m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:37 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:37:03 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:37:03 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.69354</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Near By Learning Realm International School,14, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>sujansubedi180@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.27727</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 1m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363231</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Kabita Nagarkoti</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Kabita Nagarkoti</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9841847103</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9843719521</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:35:10 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.685727</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>27.683166, 85.260317, Honda spare parts warehouse M7P6+26M, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>nagarkotikabita17@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>13:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB574</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.264285</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:34 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363231</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Kabita Nagarkoti</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Kabita Nagarkoti</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9841847103</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9843719521</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:35:10 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.685727</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>27.683166, 85.260317, Honda spare parts warehouse M7P6+26M, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>nagarkotikabita17@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>13:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>CDB574</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.264285</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6106,7 +7981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6115,7 +7990,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6143,7 +8018,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -6153,7 +8028,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -6164,7 +8039,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -6176,7 +8051,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>14h 31m</t>
+          <t>12h 42m</t>
         </is>
       </c>
     </row>
@@ -6188,7 +8063,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 59m</t>
+          <t>1d 18h 35m</t>
         </is>
       </c>
     </row>
@@ -6229,14 +8104,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -6279,14 +8154,14 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Refund Request</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -6295,97 +8170,92 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>78.9%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -6397,7 +8267,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -6415,282 +8285,194 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Refund Request</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Refundable Deposit</t>
+        </is>
+      </c>
       <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1363561</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Jiwan Kapali</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>20h 55m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6720,22 +8502,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -6745,19 +8527,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1363561</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Jiwan Kapali</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6787,22 +8569,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>08 Oct 2026 04:04:20 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -6812,19 +8594,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4d 5h 16m</t>
+          <t>20h 55m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1361677</t>
+          <t>TKT1359513</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Overseas Saving and Credit Co-operative Ltd</t>
+          <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -6839,12 +8621,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6854,44 +8636,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:39:26 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1363186</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Michael Chaudhary</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -6906,12 +8688,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -6921,54 +8703,54 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:36:39 PM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1361677</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6988,54 +8770,54 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:39:26 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1363186</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Michael Chaudhary</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7055,64 +8837,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:36:39 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1360556</t>
+          <t>TKT1360357</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Dal Bahadur Thapa</t>
+          <t>Ganesh Pokhrel</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -7122,64 +8904,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>06 Oct 2026 12:50:59 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:43:47 PM</t>
+          <t>06 Oct 2026 10:37:52 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>09 Oct 2026 01:30:16 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 39m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>3d 1h 10m</t>
+          <t>3d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1361686</t>
+          <t>TKT1360357</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Abhishek Mishra</t>
+          <t>Ganesh Pokhrel</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -7189,44 +8971,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>06 Oct 2026 12:50:59 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:15:14 AM</t>
+          <t>06 Oct 2026 10:37:52 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:30:16 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 39m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>3d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1361912</t>
+          <t>TKT1360556</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Ram Prasad Adhikari</t>
+          <t>Dal Bahadur Thapa</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7256,22 +9038,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:27:33 PM</t>
+          <t>06 Oct 2026 12:43:47 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -7281,39 +9063,39 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2d 48m</t>
+          <t>3d 1h 10m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1364308</t>
+          <t>TKT1361686</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Ritik Agrawal</t>
+          <t>Abhishek Mishra</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7323,44 +9105,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>07 Oct 2026 11:15:14 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:14 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364308</t>
+          <t>TKT1361912</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Ritik Agrawal</t>
+          <t>Ram Prasad Adhikari</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7375,12 +9157,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7390,44 +9172,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>07 Oct 2026 01:27:33 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:14 PM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>2d 48m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1362712</t>
+          <t>TKT1364308</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Shyam Gautam</t>
+          <t>Ritik Agrawal</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7442,12 +9224,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -7457,54 +9239,54 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:21:11 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 09:15:31 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:21:11 PM</t>
+          <t>09 Oct 2026 02:16:14 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 16m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 5m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1362011</t>
+          <t>TKT1364308</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Shivaraj Ojhaya  Tharu</t>
+          <t>Ritik Agrawal</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7524,44 +9306,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:57:24 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:22:05 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:41:21 PM</t>
+          <t>09 Oct 2026 02:16:14 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 43m</t>
+          <t>3h 16m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2d 19m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1363498</t>
+          <t>TKT1362712</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Unnati Hardware and suppliers</t>
+          <t>Shyam Gautam</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7591,22 +9373,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:47:31 PM</t>
+          <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:20:49 PM</t>
+          <t>07 Oct 2026 09:15:31 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:47:31 PM</t>
+          <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7616,39 +9398,39 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>23h 26m</t>
+          <t>1d 17h 5m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1363317</t>
+          <t>TKT1362011</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Amal Shrestha</t>
+          <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -7658,44 +9440,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:33:28 PM</t>
+          <t>07 Oct 2026 02:57:24 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:29 PM</t>
+          <t>07 Oct 2026 02:22:05 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:33:28 PM</t>
+          <t>09 Oct 2026 02:41:21 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 43m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 32m</t>
+          <t>2d 19m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1360970</t>
+          <t>TKT1363498</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Roshan lamichhane</t>
+          <t>Unnati Hardware and suppliers</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7725,22 +9507,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:55:06 PM</t>
+          <t>09 Oct 2026 02:47:31 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:43:34 PM</t>
+          <t>08 Oct 2026 03:20:49 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:55:06 PM</t>
+          <t>09 Oct 2026 02:47:31 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -7750,74 +9532,677 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 22h 11m</t>
+          <t>23h 26m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>TKT1363317</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Amal Shrestha</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:33:28 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:00:29 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:33:28 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360970</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Roshan lamichhane</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:55:06 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 04:43:34 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 02:55:06 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>TKT1360101</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Suman Neupane</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 02:54:41 PM</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>06 Oct 2026 07:08:33 AM</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 02:54:41 PM</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>3d 7h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364274</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Chhow Maya Tamang</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:45:40 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:18 AM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:45:40 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361815</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Mangal das shrestha</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:40 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 12:31:41 PM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:40 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>2d 3h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364471</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Sujit Shrestha</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:32:27 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:52:21 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:32:27 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>2h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363149</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>dipal shrestha</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:38:37 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:20:05 AM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:38:37 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361538</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Timsina</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Refund Request</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Refundable Deposit</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 09:57:52 AM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:36:06 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363231</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Kabita Nagarkoti</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:35:10 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363231</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Kabita Nagarkoti</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:16:31 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:35:10 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6162,10 +6162,8 @@
           <t>Chhow Maya Tamang</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9745383806</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9745383806</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6251,10 +6249,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6265,7 +6261,7 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6361,10 +6357,8 @@
           <t>Goma Adhikari</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9813097646</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9813097646</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6446,10 +6440,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -6460,7 +6452,7 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -6556,10 +6548,8 @@
           <t>Mangal das shrestha</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9742468574</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9742468574</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6594,10 +6584,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.74281</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.74281</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6653,25 +6641,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>L8-2</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.33132</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.33132000000001</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -6767,10 +6751,8 @@
           <t>Sujit Shrestha</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9849838775</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9849838775</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6805,10 +6787,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.744333</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.744333</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -6864,25 +6844,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>L1-7</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.332844</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.33284399999999</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6978,10 +6954,8 @@
           <t>dipal shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9851234306</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9851234306</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7016,10 +6990,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -7057,10 +7029,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH35" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
@@ -7079,25 +7049,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7193,10 +7159,8 @@
           <t>Saroj Timsina</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9844641620</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9844641620</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7231,10 +7195,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.71277</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.71277</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7272,10 +7234,8 @@
           <t>Refundable Deposit</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
@@ -7294,25 +7254,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>3,15</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.29517</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.29517</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7408,10 +7364,8 @@
           <t>Sujan Subedi</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9808592524</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9808592524</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7446,10 +7400,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.69354</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.69354</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7501,25 +7453,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.27727</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.27727</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7615,10 +7563,8 @@
           <t>Kabita Nagarkoti</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9841847103</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9841847103</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7653,10 +7599,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.685727</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.685727</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -7712,25 +7656,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB574</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.264285</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.264285</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7826,10 +7766,8 @@
           <t>Kabita Nagarkoti</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9841847103</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9841847103</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7864,10 +7802,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.685727</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.685727</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -7923,48 +7859,848 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>CDB574</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.264285</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.264285</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 18m</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 18m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9861850476</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:27:21 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861850476</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:57:06 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Modern Nepal College - College Sorhakhutte Bahati Pokhari Buddha Tole Marg Kathmandu 44600, Kathmand</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>9861850476@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>00:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>2h 29m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>8d 2h 38m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9861850476</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:27:21 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861850476</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:57:06 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Modern Nepal College - College Sorhakhutte Bahati Pokhari Buddha Tole Marg Kathmandu 44600, Kathmand</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>9861850476@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>00:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>2h 29m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>8d 2h 38m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359613</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9803269701</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:01:47 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803269701</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:13:23 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:01:47 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Bhadrakali English Medium School - General education school Q85W+7VJ Unnamed Road Budhanilkantha 446</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>grgashim20242@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr"/>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 48m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 3:53 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359613</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9803269701</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:01:47 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803269701</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:13:23 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:01:47 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Bhadrakali English Medium School - General education school Q85W+7VJ Unnamed Road Budhanilkantha 446</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>grgashim20242@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 48m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7981,7 +8717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8018,7 +8754,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -8028,7 +8764,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -8039,7 +8775,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8787,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12h 42m</t>
+          <t>11h 59m</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8799,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 35m</t>
+          <t>2d 5h 27m</t>
         </is>
       </c>
     </row>
@@ -8104,14 +8840,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -8248,14 +8984,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -9770,7 +10506,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -9837,7 +10573,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -9904,7 +10640,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -9971,7 +10707,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -10038,7 +10774,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -10105,7 +10841,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -10172,14 +10908,14 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 12:16:31 PM</t>
@@ -10203,6 +10939,140 @@
       <c r="M54" s="3" t="inlineStr">
         <is>
           <t>1d 3h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:27:21 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:57:06 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>2h 29m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>8d 2h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 01:27:21 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:57:06 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>2h 29m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>8d 2h 38m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -506,7 +506,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -7969,10 +7969,8 @@
           <t>Ishwori pandey</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9861850476</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9861850476</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8062,10 +8060,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -8076,7 +8072,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8172,10 +8168,8 @@
           <t>Ishwori pandey</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9861850476</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9861850476</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8265,10 +8259,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
@@ -8279,7 +8271,7 @@
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8375,10 +8367,8 @@
           <t>lok bahadur malla</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9803269701</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9803269701</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8464,10 +8454,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -8478,7 +8466,7 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8574,10 +8562,8 @@
           <t>lok bahadur malla</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9803269701</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9803269701</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8663,10 +8649,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -8677,30 +8661,1077 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>3d 23h 48m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9803334769</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9861500589</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:02:09 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.69044</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Naya Basti, Kuleshwor Height Pani Tanki, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>chiraniyagyan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB297</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.29494</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 18m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 18m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364270</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Rajin hachhethu</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Rajin hachhethu</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9843013129</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:15:38 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9862960150</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:28:08 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:15:38 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.67148</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Libali, Bhaktapur, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>rajinhachhethu2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>05:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>L17-3</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.439044</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>3d 23h 48m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>5h 47m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:14 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363190</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Ghemosu</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Ghemosu</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9861518468</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:14:21 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861518467B</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:44:31 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:14:21 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Thimi, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>Abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>14:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>L45-3</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 29m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:16 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364276</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9845998640</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9845998640</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:16:18 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.68464</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Satungal Buddha Mandir - Near Mahadhyo Parbati, Satungal , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>5333rajusharma@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>05:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Anu Bogati</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>CDB207</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.24888</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:15 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364276</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9845998640</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9845998640</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:16:18 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.68464</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Satungal Buddha Mandir - Near Mahadhyo Parbati, Satungal , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>5333rajusharma@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>05:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Anu Bogati</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB207</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.24888</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8717,7 +9748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8754,7 +9785,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -8764,7 +9795,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -8775,7 +9806,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -8787,7 +9818,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>11h 59m</t>
+          <t>10h 50m</t>
         </is>
       </c>
     </row>
@@ -8799,7 +9830,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 27m</t>
+          <t>2d 11m</t>
         </is>
       </c>
     </row>
@@ -8840,14 +9871,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -8984,14 +10015,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -10975,7 +12006,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -11042,14 +12073,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 01:27:21 PM</t>
@@ -11073,6 +12104,274 @@
       <c r="M56" s="3" t="inlineStr">
         <is>
           <t>8d 2h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364270</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Rajin hachhethu</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:15:38 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:28:08 AM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:15:38 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>5h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363190</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Ghemosu</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:14:21 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:44:31 AM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:14:21 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364276</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:16:18 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364276</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:16:18 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="39" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -8757,10 +8757,8 @@
           <t>Gyan Chiraniya</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9803334769</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9803334769</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8795,10 +8793,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.69044</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.69044</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -8850,25 +8846,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>CDB297</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.29494</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.29494</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8964,10 +8956,8 @@
           <t>Rajin hachhethu</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9843013129</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9843013129</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9002,10 +8992,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.67148</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.67148</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9061,25 +9049,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>L17-3</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.439044</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.439044</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9175,10 +9159,8 @@
           <t>Bibek Ghemosu</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9861518468</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9861518468</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9250,10 +9232,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH46" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH46" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
@@ -9272,10 +9252,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -9286,7 +9264,7 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9382,10 +9360,8 @@
           <t>Raju Sharma</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9845998640</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9845998640</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9420,10 +9396,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.68464</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.68464</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9479,25 +9453,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>CDB207</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.24888</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.24888</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9593,10 +9563,8 @@
           <t>Raju Sharma</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9845998640</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9845998640</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9631,10 +9599,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.68464</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.68464</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9690,50 +9656,866 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB207</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.24888</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.24888</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>5h 43m</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>5h 43m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT ISSUE</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362946</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9861837436</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:18 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861837436</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:40:27 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:18 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>27.72187828332493, 85.30764362100628, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>9861837436@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>16:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 38m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364350</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>OM Medlink Enterprises PVT, Ltd</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>OM Medlink Enterprises PVT, Ltd</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9849175693</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:30:42 AM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9849175693</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:30:42 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:31:21 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.671318</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Near Om pharma traders, Jagati-KamalBinayak Rd, Bhaktapur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>ompharmatraders@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>L17-1</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.438679</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:23 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359444</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9841920384</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 01:20:35 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841920384</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:10:37 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:23:59 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Agraj Group Industries Pvt. Ltd - Mineral water company P8W8+G5F Sayapatri Nagar Tokha municipality</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>9841920384@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>3d 3h 3m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>4d 2h 13m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>No internet connection</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363707</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Bhandari</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Bhandari</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9840727481</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:54 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>KLK9840727481</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:33:22 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:54 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Active Mobile Sales And Reparing Centre,Baniyatar Rd, Kathmandu, Kathmandu, Bagmati, Nepal, Nepal, K</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>9840727481@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>08:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr"/>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L33-5</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>22h 46m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -9748,13 +10530,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -9785,7 +10567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -9795,7 +10577,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -9806,7 +10588,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -9818,7 +10600,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 50m</t>
+          <t>10h 12m</t>
         </is>
       </c>
     </row>
@@ -9830,7 +10612,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
@@ -9871,14 +10653,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>26</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -9889,10 +10671,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -10015,14 +10797,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>26</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10839,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -10075,65 +10857,65 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Refund Request</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Refund Request</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Refundable Deposit</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -10142,171 +10924,127 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1363561</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Jiwan Kapali</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -10336,22 +11074,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -10361,19 +11099,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>20h 55m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1363561</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Jiwan Kapali</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -10403,22 +11141,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>08 Oct 2026 04:04:20 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -10428,19 +11166,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>20h 55m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1359513</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10470,22 +11208,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -10495,19 +11233,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>4d 5h 16m</t>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1361677</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Overseas Saving and Credit Co-operative Ltd</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -10522,12 +11260,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -10537,44 +11275,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:39:26 PM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1363186</t>
+          <t>TKT1361677</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Michael Chaudhary</t>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -10604,54 +11342,54 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:36:39 PM</t>
+          <t>09 Oct 2026 01:39:26 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1363186</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Michael Chaudhary</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -10671,32 +11409,32 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:36:39 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
     </row>
@@ -10770,32 +11508,32 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1360556</t>
+          <t>TKT1360357</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Dal Bahadur Thapa</t>
+          <t>Ganesh Pokhrel</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -10805,54 +11543,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>06 Oct 2026 12:50:59 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:43:47 PM</t>
+          <t>06 Oct 2026 10:37:52 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>09 Oct 2026 01:30:16 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 39m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>3d 1h 10m</t>
+          <t>3d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1361686</t>
+          <t>TKT1360556</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Abhishek Mishra</t>
+          <t>Dal Bahadur Thapa</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -10872,22 +11610,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:15:14 AM</t>
+          <t>06 Oct 2026 12:43:47 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -10897,29 +11635,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>3d 1h 10m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1361912</t>
+          <t>TKT1361686</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Ram Prasad Adhikari</t>
+          <t>Abhishek Mishra</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -10939,22 +11677,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:27:33 PM</t>
+          <t>07 Oct 2026 11:15:14 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -10964,19 +11702,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 48m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1364308</t>
+          <t>TKT1361912</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Ritik Agrawal</t>
+          <t>Ram Prasad Adhikari</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -10991,12 +11729,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -11006,32 +11744,32 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>07 Oct 2026 01:27:33 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:14 PM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>2d 48m</t>
         </is>
       </c>
     </row>
@@ -11105,12 +11843,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1362712</t>
+          <t>TKT1364308</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Shyam Gautam</t>
+          <t>Ritik Agrawal</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11125,12 +11863,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -11140,64 +11878,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:21:11 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 09:15:31 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:21:11 PM</t>
+          <t>09 Oct 2026 02:16:14 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 16m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 5m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1362011</t>
+          <t>TKT1362712</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Shivaraj Ojhaya  Tharu</t>
+          <t>Shyam Gautam</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -11207,64 +11945,64 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:57:24 PM</t>
+          <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:22:05 PM</t>
+          <t>07 Oct 2026 09:15:31 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:41:21 PM</t>
+          <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 19m</t>
+          <t>1d 17h 5m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1363498</t>
+          <t>TKT1362011</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Unnati Hardware and suppliers</t>
+          <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -11274,44 +12012,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:47:31 PM</t>
+          <t>07 Oct 2026 02:57:24 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:20:49 PM</t>
+          <t>07 Oct 2026 02:22:05 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:47:31 PM</t>
+          <t>09 Oct 2026 02:41:21 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 43m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>23h 26m</t>
+          <t>2d 19m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1363317</t>
+          <t>TKT1363498</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Amal Shrestha</t>
+          <t>Unnati Hardware and suppliers</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11341,22 +12079,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:33:28 PM</t>
+          <t>09 Oct 2026 02:47:31 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:29 PM</t>
+          <t>08 Oct 2026 03:20:49 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:33:28 PM</t>
+          <t>09 Oct 2026 02:47:31 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -11366,19 +12104,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 32m</t>
+          <t>23h 26m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1360970</t>
+          <t>TKT1363317</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Roshan lamichhane</t>
+          <t>Amal Shrestha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11408,22 +12146,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:55:06 PM</t>
+          <t>09 Oct 2026 02:33:28 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:43:34 PM</t>
+          <t>08 Oct 2026 01:00:29 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:55:06 PM</t>
+          <t>09 Oct 2026 02:33:28 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -11433,19 +12171,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2d 22h 11m</t>
+          <t>1d 1h 32m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1360101</t>
+          <t>TKT1360970</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Suman Neupane</t>
+          <t>Roshan lamichhane</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -11475,22 +12213,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:54:41 PM</t>
+          <t>09 Oct 2026 02:55:06 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 07:08:33 AM</t>
+          <t>06 Oct 2026 04:43:34 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:54:41 PM</t>
+          <t>09 Oct 2026 02:55:06 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -11500,19 +12238,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>3d 7h 46m</t>
+          <t>2d 22h 11m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1364274</t>
+          <t>TKT1360101</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Chhow Maya Tamang</t>
+          <t>Suman Neupane</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -11542,22 +12280,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:45:40 PM</t>
+          <t>09 Oct 2026 02:54:41 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:32:18 AM</t>
+          <t>06 Oct 2026 07:08:33 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:45:40 PM</t>
+          <t>09 Oct 2026 02:54:41 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -11567,19 +12305,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>5h 13m</t>
+          <t>3d 7h 46m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1361815</t>
+          <t>TKT1364274</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mangal das shrestha</t>
+          <t>Chhow Maya Tamang</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -11609,22 +12347,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:40 PM</t>
+          <t>09 Oct 2026 03:45:40 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 12:31:41 PM</t>
+          <t>09 Oct 2026 10:32:18 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:40 PM</t>
+          <t>09 Oct 2026 03:45:40 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -11634,19 +12372,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 10m</t>
+          <t>5h 13m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1364471</t>
+          <t>TKT1361815</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Sujit Shrestha</t>
+          <t>Mangal das shrestha</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -11681,17 +12419,17 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:32:27 PM</t>
+          <t>09 Oct 2026 03:42:40 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:52:21 PM</t>
+          <t>07 Oct 2026 12:31:41 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:32:27 PM</t>
+          <t>09 Oct 2026 03:42:40 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -11701,29 +12439,29 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2d 3h 10m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1363149</t>
+          <t>TKT1364471</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>dipal shrestha</t>
+          <t>Sujit Shrestha</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -11743,22 +12481,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:38:37 PM</t>
+          <t>09 Oct 2026 03:32:27 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:20:05 AM</t>
+          <t>09 Oct 2026 12:52:21 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:38:37 PM</t>
+          <t>09 Oct 2026 03:32:27 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -11768,29 +12506,29 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 18m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1361538</t>
+          <t>TKT1363149</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Saroj Timsina</t>
+          <t>dipal shrestha</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Refund Request</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -11810,22 +12548,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:36:06 PM</t>
+          <t>09 Oct 2026 03:38:37 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 09:57:52 AM</t>
+          <t>08 Oct 2026 11:20:05 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:36:06 PM</t>
+          <t>09 Oct 2026 03:38:37 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -11835,39 +12573,39 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 38m</t>
+          <t>1d 4h 18m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1363231</t>
+          <t>TKT1361538</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Kabita Nagarkoti</t>
+          <t>Saroj Timsina</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Refund Request</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Refundable Deposit</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -11877,32 +12615,32 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:16:31 PM</t>
+          <t>09 Oct 2026 03:36:06 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:16:31 PM</t>
+          <t>07 Oct 2026 09:57:52 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:35:10 PM</t>
+          <t>09 Oct 2026 03:36:06 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 18m</t>
+          <t>2d 5h 38m</t>
         </is>
       </c>
     </row>
@@ -11976,12 +12714,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1353940</t>
+          <t>TKT1363231</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Ishwori pandey</t>
+          <t>Kabita Nagarkoti</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -12011,32 +12749,32 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:27:21 PM</t>
+          <t>08 Oct 2026 12:16:31 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:18:49 PM</t>
+          <t>08 Oct 2026 12:16:31 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:57:06 PM</t>
+          <t>09 Oct 2026 03:35:10 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2h 29m</t>
+          <t>1d 3h 18m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>8d 2h 38m</t>
+          <t>1d 3h 18m</t>
         </is>
       </c>
     </row>
@@ -12110,12 +12848,12 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1364270</t>
+          <t>TKT1353940</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Rajin hachhethu</t>
+          <t>Ishwori pandey</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -12130,59 +12868,59 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:15:38 PM</t>
+          <t>09 Oct 2026 01:27:21 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:28:08 AM</t>
+          <t>01 Oct 2026 01:18:49 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:15:38 PM</t>
+          <t>09 Oct 2026 03:57:06 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 29m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>5h 47m</t>
+          <t>8d 2h 38m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1363190</t>
+          <t>TKT1364270</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bibek Ghemosu</t>
+          <t>Rajin hachhethu</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12207,27 +12945,27 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:14:21 PM</t>
+          <t>09 Oct 2026 04:15:38 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:44:31 AM</t>
+          <t>09 Oct 2026 10:28:08 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:14:21 PM</t>
+          <t>09 Oct 2026 04:15:38 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -12237,19 +12975,19 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 29m</t>
+          <t>5h 47m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1364276</t>
+          <t>TKT1363190</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Raju Sharma</t>
+          <t>Bibek Ghemosu</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -12264,47 +13002,47 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:32:43 AM</t>
+          <t>09 Oct 2026 04:14:21 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:32:43 AM</t>
+          <t>08 Oct 2026 11:44:31 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:16:18 PM</t>
+          <t>09 Oct 2026 04:14:21 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>5h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>5h 43m</t>
+          <t>1d 4h 29m</t>
         </is>
       </c>
     </row>
@@ -12341,37 +13079,238 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
           <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:32:43 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:16:18 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>5h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364276</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Raju Sharma</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 10:32:43 AM</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 10:32:43 AM</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 04:16:18 PM</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>5h 43m</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>5h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362946</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:18 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:40:27 AM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:18 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363707</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Kamala Bhandari</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : No internet connection   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:54 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 05:33:22 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:54 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>22h 46m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW52"/>
+  <dimension ref="A1:AW54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -9766,10 +9766,8 @@
           <t>Dinesh Lal Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9861837436</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9861837436</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9859,10 +9857,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -9873,7 +9869,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9969,10 +9965,8 @@
           <t>OM Medlink Enterprises PVT, Ltd</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9849175693</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9849175693</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10007,10 +10001,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.671318</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.671318</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10062,25 +10054,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>L17-1</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.438679</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.43867899999999</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10176,10 +10164,8 @@
           <t>Laxmi Mahat Pandey</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9841920384</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9841920384</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10265,10 +10251,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10279,7 +10263,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10375,10 +10359,8 @@
           <t>Kamala Bhandari</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9840727481</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9840727481</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10413,10 +10395,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10472,50 +10452,468 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L33-5</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>22h 46m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : No internet connection   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Router upgarde to Daul band router</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362196</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Dvi Kala Rai</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Dvi Kala Rai</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9810221273</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9810221273</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:04:29 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.65468</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Near Bhainsepati Badminton Playcourt,Trail 55, Karyabinayak, Lalitpur, Bagmati, Nepal, Nepal, Lalitp</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>salinshrestha00@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>20:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>CDB598</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.30203</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>22h 46m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2d 29m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW52" s="3" t="inlineStr">
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363197</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Romit Shahi</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Romit Shahi</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9808033657</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9808033657R</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:47:53 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.768331</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Q89J+F4G, Tokha 44600 Near by Tokha Ganeshthan Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>shahiromit29@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>14:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L26-2</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.329899</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 46m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10567,7 +10965,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -10577,7 +10975,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10588,7 +10986,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10998,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10h 12m</t>
+          <t>9h 38m</t>
         </is>
       </c>
     </row>
@@ -10612,7 +11010,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 22h 28m</t>
         </is>
       </c>
     </row>
@@ -10653,14 +11051,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.8%</t>
         </is>
       </c>
     </row>
@@ -10797,26 +11195,26 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -10839,7 +11237,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -10862,14 +11260,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -10880,65 +11278,65 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Refund Request</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Refund Request</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Refundable Deposit</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -10947,171 +11345,127 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364290</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Carpenter Hardwares Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 10:44:56 AM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:33:20 PM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>1h 48m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1363561</t>
+          <t>TKT1364290</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Jiwan Kapali</t>
+          <t>Carpenter Hardwares Pvt.Ltd.</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -11141,22 +11495,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 04:04:20 PM</t>
+          <t>09 Oct 2026 10:44:56 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:59:31 PM</t>
+          <t>09 Oct 2026 12:33:20 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -11166,19 +11520,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>20h 55m</t>
+          <t>1h 48m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1359513</t>
+          <t>TKT1363561</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Laxmi Chhetri Baniya</t>
+          <t>Jiwan Kapali</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -11208,22 +11562,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:03:46 PM</t>
+          <t>08 Oct 2026 04:04:20 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:53:37 PM</t>
+          <t>09 Oct 2026 12:59:31 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -11233,19 +11587,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 49m</t>
+          <t>20h 55m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1358878</t>
+          <t>TKT1359513</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Tanisha giri</t>
+          <t>Laxmi Chhetri Baniya</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -11275,22 +11629,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 08:09:51 AM</t>
+          <t>05 Oct 2026 03:03:46 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:26:08 PM</t>
+          <t>09 Oct 2026 12:53:37 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -11300,19 +11654,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>4d 5h 16m</t>
+          <t>3d 21h 49m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1361677</t>
+          <t>TKT1358878</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Overseas Saving and Credit Co-operative Ltd</t>
+          <t>Tanisha giri</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -11327,12 +11681,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -11342,44 +11696,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:11:48 AM</t>
+          <t>05 Oct 2026 08:09:51 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:39:26 PM</t>
+          <t>09 Oct 2026 01:26:08 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 27m</t>
+          <t>4d 5h 16m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1363186</t>
+          <t>TKT1361677</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Michael Chaudhary</t>
+          <t>Overseas Saving and Credit Co-operative Ltd</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -11409,54 +11763,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6 Router   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:42:07 AM</t>
+          <t>07 Oct 2026 11:11:48 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:36:39 PM</t>
+          <t>09 Oct 2026 01:39:26 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 54m</t>
+          <t>2d 2h 27m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1360357</t>
+          <t>TKT1363186</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Pokhrel</t>
+          <t>Michael Chaudhary</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -11476,32 +11830,32 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:50:59 PM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:37:52 AM</t>
+          <t>08 Oct 2026 11:42:07 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:30:16 PM</t>
+          <t>09 Oct 2026 01:36:39 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>3d 39m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>3d 2h 52m</t>
+          <t>1d 1h 54m</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11929,32 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1360556</t>
+          <t>TKT1360357</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Dal Bahadur Thapa</t>
+          <t>Ganesh Pokhrel</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -11610,54 +11964,54 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : slow issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>06 Oct 2026 12:50:59 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 12:43:47 PM</t>
+          <t>06 Oct 2026 10:37:52 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:53:50 PM</t>
+          <t>09 Oct 2026 01:30:16 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3d 39m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>3d 1h 10m</t>
+          <t>3d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1361686</t>
+          <t>TKT1360556</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Abhishek Mishra</t>
+          <t>Dal Bahadur Thapa</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -11677,22 +12031,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:15:14 AM</t>
+          <t>06 Oct 2026 12:43:47 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:07:14 PM</t>
+          <t>09 Oct 2026 01:53:50 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -11702,29 +12056,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>3d 1h 10m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1361912</t>
+          <t>TKT1361686</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Ram Prasad Adhikari</t>
+          <t>Abhishek Mishra</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -11744,22 +12098,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : ssid not shown   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 01:27:33 PM</t>
+          <t>07 Oct 2026 11:15:14 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:06 PM</t>
+          <t>09 Oct 2026 02:07:14 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -11769,19 +12123,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 48m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1364308</t>
+          <t>TKT1361912</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Ritik Agrawal</t>
+          <t>Ram Prasad Adhikari</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -11796,12 +12150,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -11811,32 +12165,32 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:59:15 AM</t>
+          <t>07 Oct 2026 01:27:33 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:16:14 PM</t>
+          <t>09 Oct 2026 02:16:06 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>3h 16m</t>
+          <t>2d 48m</t>
         </is>
       </c>
     </row>
@@ -11910,12 +12264,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1362712</t>
+          <t>TKT1364308</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Shyam Gautam</t>
+          <t>Ritik Agrawal</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -11930,12 +12284,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -11945,64 +12299,64 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:21:11 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 09:15:31 PM</t>
+          <t>09 Oct 2026 10:59:15 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:21:11 PM</t>
+          <t>09 Oct 2026 02:16:14 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>3h 16m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 17h 5m</t>
+          <t>3h 16m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1362011</t>
+          <t>TKT1362712</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Shivaraj Ojhaya  Tharu</t>
+          <t>Shyam Gautam</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -12012,64 +12366,64 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:57:24 PM</t>
+          <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:22:05 PM</t>
+          <t>07 Oct 2026 09:15:31 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:41:21 PM</t>
+          <t>09 Oct 2026 02:21:11 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 19m</t>
+          <t>1d 17h 5m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1363498</t>
+          <t>TKT1362011</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Unnati Hardware and suppliers</t>
+          <t>Shivaraj Ojhaya  Tharu</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -12079,44 +12433,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : stbbox issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:47:31 PM</t>
+          <t>07 Oct 2026 02:57:24 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 03:20:49 PM</t>
+          <t>07 Oct 2026 02:22:05 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:47:31 PM</t>
+          <t>09 Oct 2026 02:41:21 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 23h 43m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>23h 26m</t>
+          <t>2d 19m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1363317</t>
+          <t>TKT1363498</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Amal Shrestha</t>
+          <t>Unnati Hardware and suppliers</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12146,22 +12500,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:33:28 PM</t>
+          <t>09 Oct 2026 02:47:31 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:00:29 PM</t>
+          <t>08 Oct 2026 03:20:49 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:33:28 PM</t>
+          <t>09 Oct 2026 02:47:31 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -12171,19 +12525,19 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 32m</t>
+          <t>23h 26m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1360970</t>
+          <t>TKT1363317</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Roshan lamichhane</t>
+          <t>Amal Shrestha</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -12213,22 +12567,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:55:06 PM</t>
+          <t>09 Oct 2026 02:33:28 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 04:43:34 PM</t>
+          <t>08 Oct 2026 01:00:29 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:55:06 PM</t>
+          <t>09 Oct 2026 02:33:28 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -12238,19 +12592,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2d 22h 11m</t>
+          <t>1d 1h 32m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1360101</t>
+          <t>TKT1360970</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Suman Neupane</t>
+          <t>Roshan lamichhane</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12280,22 +12634,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:54:41 PM</t>
+          <t>09 Oct 2026 02:55:06 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 07:08:33 AM</t>
+          <t>06 Oct 2026 04:43:34 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 02:54:41 PM</t>
+          <t>09 Oct 2026 02:55:06 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -12305,19 +12659,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>3d 7h 46m</t>
+          <t>2d 22h 11m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1364274</t>
+          <t>TKT1360101</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Chhow Maya Tamang</t>
+          <t>Suman Neupane</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -12347,22 +12701,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>Case : POWER ISSUE  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:45:40 PM</t>
+          <t>09 Oct 2026 02:54:41 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:32:18 AM</t>
+          <t>06 Oct 2026 07:08:33 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:45:40 PM</t>
+          <t>09 Oct 2026 02:54:41 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -12372,19 +12726,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>5h 13m</t>
+          <t>3d 7h 46m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1361815</t>
+          <t>TKT1364274</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Mangal das shrestha</t>
+          <t>Chhow Maya Tamang</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12414,22 +12768,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:40 PM</t>
+          <t>09 Oct 2026 03:45:40 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 12:31:41 PM</t>
+          <t>09 Oct 2026 10:32:18 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:42:40 PM</t>
+          <t>09 Oct 2026 03:45:40 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -12439,19 +12793,19 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2d 3h 10m</t>
+          <t>5h 13m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1364471</t>
+          <t>TKT1361815</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Sujit Shrestha</t>
+          <t>Mangal das shrestha</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -12486,17 +12840,17 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:32:27 PM</t>
+          <t>09 Oct 2026 03:42:40 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:52:21 PM</t>
+          <t>07 Oct 2026 12:31:41 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:32:27 PM</t>
+          <t>09 Oct 2026 03:42:40 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -12506,29 +12860,29 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2h 40m</t>
+          <t>2d 3h 10m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1363149</t>
+          <t>TKT1364471</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>dipal shrestha</t>
+          <t>Sujit Shrestha</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -12548,22 +12902,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:38:37 PM</t>
+          <t>09 Oct 2026 03:32:27 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:20:05 AM</t>
+          <t>09 Oct 2026 12:52:21 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:38:37 PM</t>
+          <t>09 Oct 2026 03:32:27 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -12573,29 +12927,29 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 18m</t>
+          <t>2h 40m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1361538</t>
+          <t>TKT1363149</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Saroj Timsina</t>
+          <t>dipal shrestha</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Refund Request</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -12615,22 +12969,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
+          <t>Case : SLOW ISSUE   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:36:06 PM</t>
+          <t>09 Oct 2026 03:38:37 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 09:57:52 AM</t>
+          <t>08 Oct 2026 11:20:05 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:36:06 PM</t>
+          <t>09 Oct 2026 03:38:37 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -12640,39 +12994,39 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>2d 5h 38m</t>
+          <t>1d 4h 18m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1363231</t>
+          <t>TKT1361538</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Kabita Nagarkoti</t>
+          <t>Saroj Timsina</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Refund Request</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Refundable Deposit</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -12682,32 +13036,32 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Device recovery   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:16:31 PM</t>
+          <t>09 Oct 2026 03:36:06 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 12:16:31 PM</t>
+          <t>07 Oct 2026 09:57:52 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:35:10 PM</t>
+          <t>09 Oct 2026 03:36:06 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 18m</t>
+          <t>2d 5h 38m</t>
         </is>
       </c>
     </row>
@@ -12781,12 +13135,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1353940</t>
+          <t>TKT1363231</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Ishwori pandey</t>
+          <t>Kabita Nagarkoti</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12816,32 +13170,32 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 01:27:21 PM</t>
+          <t>08 Oct 2026 12:16:31 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 01:18:49 PM</t>
+          <t>08 Oct 2026 12:16:31 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:57:06 PM</t>
+          <t>09 Oct 2026 03:35:10 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2h 29m</t>
+          <t>1d 3h 18m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>8d 2h 38m</t>
+          <t>1d 3h 18m</t>
         </is>
       </c>
     </row>
@@ -12915,12 +13269,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1364270</t>
+          <t>TKT1353940</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Rajin hachhethu</t>
+          <t>Ishwori pandey</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12935,12 +13289,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -12950,44 +13304,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:15:38 PM</t>
+          <t>09 Oct 2026 01:27:21 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:28:08 AM</t>
+          <t>01 Oct 2026 01:18:49 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:15:38 PM</t>
+          <t>09 Oct 2026 03:57:06 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 29m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>5h 47m</t>
+          <t>8d 2h 38m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1363190</t>
+          <t>TKT1364270</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Bibek Ghemosu</t>
+          <t>Rajin hachhethu</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -13022,17 +13376,17 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:14:21 PM</t>
+          <t>09 Oct 2026 04:15:38 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 11:44:31 AM</t>
+          <t>09 Oct 2026 10:28:08 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:14:21 PM</t>
+          <t>09 Oct 2026 04:15:38 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -13042,19 +13396,19 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1d 4h 29m</t>
+          <t>5h 47m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1364276</t>
+          <t>TKT1363190</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Raju Sharma</t>
+          <t>Bibek Ghemosu</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -13069,12 +13423,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -13084,32 +13438,32 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:32:43 AM</t>
+          <t>09 Oct 2026 04:14:21 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:32:43 AM</t>
+          <t>08 Oct 2026 11:44:31 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:16:18 PM</t>
+          <t>09 Oct 2026 04:14:21 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>5h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>5h 43m</t>
+          <t>1d 4h 29m</t>
         </is>
       </c>
     </row>
@@ -13183,134 +13537,335 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1362946</t>
+          <t>TKT1364276</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Dinesh Lal Shrestha</t>
+          <t>Raju Sharma</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+          <t>Case :  wifi 6 router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:19:18 PM</t>
+          <t>09 Oct 2026 10:32:43 AM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 09:40:27 AM</t>
+          <t>09 Oct 2026 10:32:43 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:19:18 PM</t>
+          <t>09 Oct 2026 04:16:18 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 43m</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 38m</t>
+          <t>5h 43m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>TKT1362946</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Dinesh Lal Shrestha</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT ISSUE   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:18 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 09:40:27 AM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:19:18 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
           <t>TKT1363707</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Kamala Bhandari</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Case : No internet connection   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : No internet connection   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 04:19:54 PM</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 05:33:22 PM</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 04:19:54 PM</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr">
         <is>
           <t>22h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362196</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Dvi Kala Rai</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 04:04:29 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>2d 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363197</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Romit Shahi</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:47:53 AM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:54 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 46m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW54"/>
+  <dimension ref="A1:AW56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10562,10 +10562,8 @@
           <t>Dvi Kala Rai</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9810221273</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9810221273</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10600,10 +10598,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.65468</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.65468</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10659,25 +10655,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>CDB598</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.30203</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.30203</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -10773,10 +10765,8 @@
           <t>Romit Shahi</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9808033657</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9808033657</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10811,10 +10801,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.768331</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.768331</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -10870,48 +10858,458 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>L26-2</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.329899</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.329899</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 46m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS54" s="3" t="inlineStr">
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:49 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359444</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9841920384</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:48 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841920384</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:10:37 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:48 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Agraj Group Industries Pvt. Ltd - Mineral water company P8W8+G5F Sayapatri Nagar Tokha municipality</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>9841920384@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>18:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 46m</t>
-        </is>
-      </c>
-      <c r="AU54" s="3" t="inlineStr">
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>4d 2h 39m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV54" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW54" s="3" t="inlineStr">
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 4:50 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364350</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>OM Medlink Enterprises PVT, Ltd</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>OM Medlink Enterprises PVT, Ltd</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9849175693</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:50:48 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9849175693</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:30:42 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:50:48 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.671318</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Near Om pharma traders, Jagati-KamalBinayak Rd, Bhaktapur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>ompharmatraders@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>05:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L17-1</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.438679</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>5h 20m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -10928,7 +11326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10965,7 +11363,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -10975,7 +11373,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -10986,7 +11384,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11396,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 38m</t>
+          <t>9h 7m</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11408,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 28m</t>
+          <t>1d 22h 45m</t>
         </is>
       </c>
     </row>
@@ -11051,14 +11449,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
     </row>
@@ -11195,14 +11593,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -13768,7 +14166,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgarde to Daul band router  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -13835,14 +14233,14 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 04:33:54 PM</t>
@@ -13866,6 +14264,140 @@
       <c r="M66" s="3" t="inlineStr">
         <is>
           <t>1d 4h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359444</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Laxmi Mahat Pandey</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:48 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 02:10:37 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:48 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>4d 2h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364350</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>OM Medlink Enterprises PVT, Ltd</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:50:48 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 11:30:42 AM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:50:48 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>5h 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW56"/>
+  <dimension ref="A1:AW59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10968,10 +10968,8 @@
           <t>Laxmi Mahat Pandey</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9841920384</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9841920384</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11061,10 +11059,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -11075,7 +11071,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11171,10 +11167,8 @@
           <t>OM Medlink Enterprises PVT, Ltd</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9849175693</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9849175693</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11209,10 +11203,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.671318</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.671318</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11268,48 +11260,673 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L17-1</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.438679</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.43867899999999</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>5h 20m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 5:15 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357726</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Kandel</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Kandel</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9865125447</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:15:36 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9865125447</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:41:13 AM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:15:30 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.66369</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>27.6636820, 85.3381038 , Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>sudipkandel55@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>23:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.33823</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>Negative Time</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>5d 5h 34m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 5:07 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363797</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Soni</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Soni</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9804233430</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:07:42 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9804233430</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 07:13:16 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:07:42 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.709164</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Near pipalbot, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr"/>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>07:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.305129</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>5h 20m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 5:06 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363780</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Karan Khadgi</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Karan Khadgi</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9803031028</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:06:51 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9803031028</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:54:29 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:06:51 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.709222</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Near Machhapuchhre Bank Limited P75X+MHP, Raja Birendra Marg, Kathmandu 44600 , Bagmati, Central, Ne</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr"/>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>08:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.302312</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>22h 12m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -11326,7 +11943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11363,7 +11980,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -11373,7 +11990,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -11384,7 +12001,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -11396,7 +12013,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>9h 7m</t>
+          <t>8h 27m</t>
         </is>
       </c>
     </row>
@@ -11408,7 +12025,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 45m</t>
+          <t>1d 23h 28m</t>
         </is>
       </c>
     </row>
@@ -11449,14 +12066,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -11593,14 +12210,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14917,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -14367,14 +14984,14 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 04:50:48 PM</t>
@@ -14398,6 +15015,207 @@
       <c r="M68" s="3" t="inlineStr">
         <is>
           <t>5h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357726</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Sudip Kandel</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:15:36 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:41:13 AM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:15:30 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Negative Time</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>5d 5h 34m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363797</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Soni</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:07:42 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 07:13:16 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:07:42 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>21h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363780</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Karan Khadgi</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:06:51 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 06:54:29 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:06:51 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>22h 12m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW59"/>
+  <dimension ref="A1:AW61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -11370,10 +11370,8 @@
           <t>Sudip Kandel</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9865125447</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9865125447</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11408,10 +11406,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.66369</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.66369</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -11467,25 +11463,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.33823</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.33823</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -11581,10 +11573,8 @@
           <t>Suresh Soni</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9804233430</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9804233430</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -11619,10 +11609,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.709164</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.709164</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -11674,25 +11662,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>85.305129</t>
-        </is>
+      <c r="AP58" s="3" t="n">
+        <v>85.30512899999999</v>
       </c>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -11778,20 +11762,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="3" t="inlineStr">
         <is>
           <t>Karan Khadgi</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9803031028</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9803031028</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11826,10 +11804,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.709222</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.709222</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -11863,10 +11839,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH59" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH59" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
@@ -11885,50 +11859,456 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.302312</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.302312</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>22h 12m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS59" s="3" t="inlineStr">
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 5:30 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363420</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Neha Rajthala</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Neha Rajthala</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9808623374</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:30:18 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9808623374</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:22:10 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:30:18 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>27.65757</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Naya thimi M9HJ+778, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr"/>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>13:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>85.38664</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
-          <t>22h 12m</t>
-        </is>
-      </c>
-      <c r="AU59" s="3" t="inlineStr">
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 8m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV59" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW59" s="3" t="inlineStr">
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 5:28 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363261</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Dhanajay kapri</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Dhanajay kapri</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9849047546</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:28:05 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9849047546</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:33:09 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:28:05 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr"/>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Sukedhara	Bigmart	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr"/>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>14:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>L60-1</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr"/>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 54m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -11943,7 +12323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11980,7 +12360,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -11990,7 +12370,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -12001,7 +12381,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12393,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 27m</t>
+          <t>8h 4m</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12405,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 28m</t>
+          <t>1d 22h 34m</t>
         </is>
       </c>
     </row>
@@ -12066,14 +12446,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -12084,10 +12464,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -12210,14 +12590,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -12256,10 +12636,10 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -15051,7 +15431,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -15118,7 +15498,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -15185,14 +15565,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 05:06:51 PM</t>
@@ -15216,6 +15596,140 @@
       <c r="M71" s="5" t="inlineStr">
         <is>
           <t>22h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363420</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Neha Rajthala</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:30:18 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 02:22:10 PM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:30:18 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363261</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Dhanajay kapri</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:28:05 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:33:09 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:28:05 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11969,10 +11969,8 @@
           <t>Neha Rajthala</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9808623374</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9808623374</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12007,10 +12005,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>27.65757</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>27.65757</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -12044,10 +12040,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH60" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH60" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
@@ -12066,25 +12060,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>85.38664</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>85.38664</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -12180,10 +12170,8 @@
           <t>Dhanajay kapri</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9849047546</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9849047546</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -12269,10 +12257,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
@@ -12283,7 +12269,7 @@
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
@@ -12332,7 +12318,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -15632,7 +15618,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -15699,7 +15685,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW61"/>
+  <dimension ref="A1:AW62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12298,6 +12298,209 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 5:48 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363128</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Rita Karanjit</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Rita Karanjit</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9843536102</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:12:10 AM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9843536102</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:12:10 AM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:48 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr"/>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Near Santoshi Mata Temple, M7WQ+PH7 Ravi Bhawan, Ganeshman Road, Kathmandu 44600, Bagmati, Nepal, Ne</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr">
+        <is>
+          <t>ritakaranjit05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>16:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr"/>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12309,7 +12512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12318,7 +12521,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12346,7 +12549,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -12356,7 +12559,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -12367,7 +12570,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12582,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 4m</t>
+          <t>8h 34m</t>
         </is>
       </c>
     </row>
@@ -12391,7 +12594,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 34m</t>
+          <t>1d 22h 12m</t>
         </is>
       </c>
     </row>
@@ -12432,14 +12635,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -12576,14 +12779,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.6%</t>
         </is>
       </c>
     </row>
@@ -15719,6 +15922,73 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363128</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Rita Karanjit</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:12:10 AM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 11:12:10 AM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:48:48 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 36m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 36m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW62"/>
+  <dimension ref="A1:AW64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12365,10 +12365,8 @@
           <t>Rita Karanjit</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9843536102</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9843536102</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -12458,10 +12456,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
@@ -12472,30 +12468,440 @@
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 36m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS62" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 36m</t>
-        </is>
-      </c>
-      <c r="AT62" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 36m</t>
-        </is>
-      </c>
-      <c r="AU62" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV62" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 6:17 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362188</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra Shake</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Rajendra Shake</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9841584881</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:17:06 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9841584881</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:57:45 PM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:17:06 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Indra Chowk Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr"/>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>22:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr"/>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 19m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 6:07 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363940</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Subedi Dhakal</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Subedi Dhakal</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9849117256</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:07:18 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9842464249</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:13:22 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:07:18 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.73782</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>machhapokhari , Amnesty International Nepal  Basanta Nagar Rd, Kathmandu 44600  27.73764, 85.30803</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>shree4subadi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>08:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.3081</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>19h 53m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -12512,7 +12918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12549,7 +12955,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -12559,7 +12965,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -12570,7 +12976,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12988,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 34m</t>
+          <t>8h 12m</t>
         </is>
       </c>
     </row>
@@ -12594,7 +13000,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 12m</t>
+          <t>1d 21h 43m</t>
         </is>
       </c>
     </row>
@@ -12635,14 +13041,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -12779,14 +13185,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -15955,14 +16361,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>08 Oct 2026 11:12:10 AM</t>
@@ -15986,6 +16392,140 @@
       <c r="M74" s="3" t="inlineStr">
         <is>
           <t>1d 6h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362188</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Rajendra Shake</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:17:06 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:57:45 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:17:06 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 19m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363940</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Subedi Dhakal</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:07:18 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:13:22 PM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:07:18 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>19h 53m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12564,10 +12564,8 @@
           <t>Rajendra Shake</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9841584881</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9841584881</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -12653,10 +12651,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
@@ -12667,7 +12663,7 @@
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -12763,10 +12759,8 @@
           <t>Srijana Subedi Dhakal</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9849117256</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9849117256</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -12801,10 +12795,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.73782</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.73782</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -12860,25 +12852,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.3081</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.3081</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
@@ -12927,7 +12915,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -16428,7 +16416,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -16495,7 +16483,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW64"/>
+  <dimension ref="A1:AW65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12895,6 +12895,209 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 7:14 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363246</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Shah</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Shah</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9841384832</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:14:12 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>9841384832</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:24:38 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:14:12 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>27.720862, 85.375933, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr"/>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>16:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>L52-3</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr"/>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 49m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12906,7 +13109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12915,7 +13118,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12943,7 +13146,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -12953,7 +13156,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -12964,7 +13167,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -12976,7 +13179,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>8h 12m</t>
+          <t>8h 2m</t>
         </is>
       </c>
     </row>
@@ -12988,7 +13191,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 43m</t>
+          <t>1d 21h 24m</t>
         </is>
       </c>
     </row>
@@ -13029,14 +13232,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -13173,14 +13376,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -16517,6 +16720,73 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363246</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Niraj Shah</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:14:12 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 12:24:38 PM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:14:12 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 49m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_09_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_09_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12962,10 +12962,8 @@
           <t>Niraj Shah</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9841384832</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9841384832</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -13033,10 +13031,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH65" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH65" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
@@ -13055,10 +13051,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -13069,7 +13063,7 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
@@ -13118,7 +13112,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -16753,7 +16747,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
